--- a/docs/downloads/04/tbl_other_act_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_other_act_alaotra_tous.xlsx
@@ -405,12 +405,6 @@
           <t>Commerçant</t>
         </is>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -441,12 +435,6 @@
           <t>Éleveur</t>
         </is>
       </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>2.1</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -459,12 +447,6 @@
           <t>Étudiant</t>
         </is>
       </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>2.1</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -567,12 +549,6 @@
           <t>Éleveur</t>
         </is>
       </c>
-      <c r="C12">
-        <v>3</v>
-      </c>
-      <c r="D12">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -801,12 +777,6 @@
           <t>Pêcheur exploitant</t>
         </is>
       </c>
-      <c r="C25">
-        <v>3</v>
-      </c>
-      <c r="D25">
-        <v>2.1</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -855,12 +825,6 @@
           <t>Chômeur</t>
         </is>
       </c>
-      <c r="C28">
-        <v>3</v>
-      </c>
-      <c r="D28">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -873,12 +837,6 @@
           <t>Commerçant</t>
         </is>
       </c>
-      <c r="C29">
-        <v>3</v>
-      </c>
-      <c r="D29">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1017,12 +975,6 @@
           <t>Ouvrier agricole</t>
         </is>
       </c>
-      <c r="C37">
-        <v>2</v>
-      </c>
-      <c r="D37">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1035,12 +987,6 @@
           <t>Éleveur</t>
         </is>
       </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-      <c r="D38">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1161,12 +1107,6 @@
           <t>Éleveur</t>
         </is>
       </c>
-      <c r="C45">
-        <v>3</v>
-      </c>
-      <c r="D45">
-        <v>1.2</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1394,12 +1334,6 @@
         <is>
           <t>Pêcheur exploitant</t>
         </is>
-      </c>
-      <c r="C58">
-        <v>3</v>
-      </c>
-      <c r="D58">
-        <v>0.2</v>
       </c>
     </row>
     <row r="59">

--- a/docs/downloads/04/tbl_other_act_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_other_act_alaotra_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,14 +384,8 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>52</v>
-      </c>
-      <c r="D2">
-        <v>55.3</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -402,7 +396,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
     </row>
@@ -414,14 +408,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C4">
         <v>37</v>
       </c>
       <c r="D4">
-        <v>39.4</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5">
@@ -432,7 +426,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Éleveur</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
     </row>
@@ -444,7 +438,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
     </row>
@@ -456,14 +450,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="C7">
-        <v>129</v>
+        <v>10</v>
       </c>
       <c r="D7">
-        <v>62.6</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="8">
@@ -474,14 +468,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D8">
-        <v>2.9</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="9">
@@ -492,14 +486,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C9">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D9">
-        <v>6.3</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="10">
@@ -510,14 +504,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="C10">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D10">
-        <v>10.7</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="11">
@@ -528,14 +522,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="C11">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D11">
-        <v>11.7</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="12">
@@ -546,8 +540,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Éleveur</t>
-        </is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>24</v>
+      </c>
+      <c r="D12">
+        <v>23.8</v>
       </c>
     </row>
     <row r="13">
@@ -558,14 +558,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="C13">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D13">
-        <v>4.4</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="14">
@@ -576,14 +576,8 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>90</v>
-      </c>
-      <c r="D14">
-        <v>54.2</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -594,14 +588,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="C15">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D15">
-        <v>4.8</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="16">
@@ -612,14 +606,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C16">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="D16">
-        <v>6</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="17">
@@ -630,14 +624,8 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="C17">
-        <v>43</v>
-      </c>
-      <c r="D17">
-        <v>25.9</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -648,14 +636,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="C18">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D18">
-        <v>6</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="19">
@@ -666,32 +654,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="C19">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D19">
-        <v>3</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="C20">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="D20">
-        <v>57.5</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="21">
@@ -702,14 +690,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="C21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D21">
-        <v>4.1</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="22">
@@ -720,14 +708,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="C22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D22">
-        <v>4.8</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="23">
@@ -738,14 +726,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C23">
         <v>27</v>
       </c>
       <c r="D23">
-        <v>18.5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24">
@@ -756,14 +744,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="C24">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D24">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -774,8 +762,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pêcheur exploitant</t>
-        </is>
+          <t>Elève / Etudiant</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>5</v>
+      </c>
+      <c r="D25">
+        <v>6.7</v>
       </c>
     </row>
     <row r="26">
@@ -786,32 +780,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="C26">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D26">
-        <v>3.4</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="C27">
-        <v>82</v>
+        <v>9</v>
       </c>
       <c r="D27">
-        <v>60.3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
@@ -822,7 +816,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
     </row>
@@ -834,7 +828,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
     </row>
@@ -846,14 +840,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C30">
         <v>37</v>
       </c>
       <c r="D30">
-        <v>27.2</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="31">
@@ -864,14 +858,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="C31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D31">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="32">
@@ -882,32 +876,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="C32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D32">
-        <v>3.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="C33">
-        <v>140</v>
+        <v>11</v>
       </c>
       <c r="D33">
-        <v>56.5</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="34">
@@ -918,14 +912,8 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Chômeur</t>
-        </is>
-      </c>
-      <c r="C34">
-        <v>10</v>
-      </c>
-      <c r="D34">
-        <v>4</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -936,14 +924,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="C35">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D35">
-        <v>4.8</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="36">
@@ -954,14 +942,14 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C36">
         <v>78</v>
       </c>
       <c r="D36">
-        <v>31.5</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37">
@@ -972,8 +960,14 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>5</v>
+      </c>
+      <c r="D37">
+        <v>4.2</v>
       </c>
     </row>
     <row r="38">
@@ -984,8 +978,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Éleveur</t>
-        </is>
+          <t>Elève / Etudiant</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>5</v>
+      </c>
+      <c r="D38">
+        <v>4.2</v>
       </c>
     </row>
     <row r="39">
@@ -996,32 +996,26 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Étudiant</t>
-        </is>
-      </c>
-      <c r="C39">
-        <v>5</v>
-      </c>
-      <c r="D39">
-        <v>2</v>
+          <t>Ouvrier agricole</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="C40">
-        <v>129</v>
+        <v>15</v>
       </c>
       <c r="D40">
-        <v>51.6</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="41">
@@ -1032,14 +1026,8 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Chômeur</t>
-        </is>
-      </c>
-      <c r="C41">
-        <v>6</v>
-      </c>
-      <c r="D41">
-        <v>2.4</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -1050,14 +1038,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="C42">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D42">
-        <v>4.8</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="43">
@@ -1068,14 +1056,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C43">
         <v>77</v>
       </c>
       <c r="D43">
-        <v>30.8</v>
+        <v>57</v>
       </c>
     </row>
     <row r="44">
@@ -1086,14 +1074,8 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="C44">
-        <v>15</v>
-      </c>
-      <c r="D44">
-        <v>6</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -1104,8 +1086,14 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Éleveur</t>
-        </is>
+          <t>Elève / Etudiant</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>8</v>
+      </c>
+      <c r="D45">
+        <v>5.9</v>
       </c>
     </row>
     <row r="46">
@@ -1116,32 +1104,32 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="C46">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D46">
-        <v>3.2</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="C47">
-        <v>121</v>
+        <v>13</v>
       </c>
       <c r="D47">
-        <v>54.8</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="48">
@@ -1152,14 +1140,8 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Chômeur</t>
-        </is>
-      </c>
-      <c r="C48">
-        <v>7</v>
-      </c>
-      <c r="D48">
-        <v>3.2</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -1170,14 +1152,14 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="C49">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D49">
-        <v>2.7</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="50">
@@ -1188,14 +1170,14 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C50">
         <v>70</v>
       </c>
       <c r="D50">
-        <v>31.7</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="51">
@@ -1206,14 +1188,8 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="C51">
-        <v>5</v>
-      </c>
-      <c r="D51">
-        <v>2.3</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -1224,50 +1200,50 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="C52">
         <v>12</v>
       </c>
       <c r="D52">
-        <v>5.4</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="C53">
-        <v>827</v>
+        <v>5</v>
       </c>
       <c r="D53">
-        <v>56.4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="C54">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="D54">
-        <v>3.1</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="55">
@@ -1278,14 +1254,14 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="C55">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="D55">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="56">
@@ -1296,14 +1272,14 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="C56">
-        <v>391</v>
+        <v>73</v>
       </c>
       <c r="D56">
-        <v>26.7</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="57">
@@ -1314,14 +1290,14 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C57">
-        <v>76</v>
+        <v>391</v>
       </c>
       <c r="D57">
-        <v>5.2</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="58">
@@ -1332,8 +1308,14 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Pêcheur exploitant</t>
-        </is>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>35</v>
+      </c>
+      <c r="D58">
+        <v>4.7</v>
       </c>
     </row>
     <row r="59">
@@ -1344,14 +1326,14 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Éleveur</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="C59">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="D59">
-        <v>0.6</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="60">
@@ -1362,14 +1344,32 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="C60">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="D60">
-        <v>3.5</v>
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>84</v>
+      </c>
+      <c r="D61">
+        <v>11.4</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/04/tbl_other_act_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_other_act_alaotra_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -391,7 +391,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -403,7 +403,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -421,7 +421,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -433,7 +433,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -445,7 +445,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -463,7 +463,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -481,7 +481,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -499,7 +499,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -517,7 +517,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -571,7 +571,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -583,7 +583,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -601,7 +601,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -619,7 +619,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -649,7 +649,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -667,7 +667,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -685,7 +685,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -703,7 +703,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -757,7 +757,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -775,7 +775,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -823,7 +823,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -835,7 +835,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -871,7 +871,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -889,7 +889,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -907,7 +907,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -919,7 +919,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -937,7 +937,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -955,7 +955,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -973,7 +973,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1003,7 +1003,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1021,7 +1021,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1033,7 +1033,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1051,7 +1051,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1069,7 +1069,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1099,7 +1099,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1117,7 +1117,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1165,7 +1165,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1183,7 +1183,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1195,7 +1195,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1213,7 +1213,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1231,7 +1231,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1249,7 +1249,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1267,7 +1267,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1285,7 +1285,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1321,7 +1321,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1339,7 +1339,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1357,7 +1357,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">

--- a/docs/downloads/04/tbl_other_act_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_other_act_alaotra_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -540,14 +540,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Inactif / Retraité</t>
         </is>
       </c>
       <c r="C12">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="D12">
-        <v>23.8</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="13">
@@ -558,26 +558,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="C13">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D13">
-        <v>11.9</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ambodivoara</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
-        </is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>6</v>
+      </c>
+      <c r="D14">
+        <v>5.9</v>
       </c>
     </row>
     <row r="15">
@@ -588,14 +594,8 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>12</v>
-      </c>
-      <c r="D15">
-        <v>13.5</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -606,14 +606,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="C16">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="D16">
-        <v>48.3</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="17">
@@ -624,8 +624,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>43</v>
+      </c>
+      <c r="D17">
+        <v>48.3</v>
       </c>
     </row>
     <row r="18">
@@ -636,14 +642,8 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Elève / Etudiant</t>
-        </is>
-      </c>
-      <c r="C18">
-        <v>5</v>
-      </c>
-      <c r="D18">
-        <v>5.6</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -654,14 +654,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="C19">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D19">
-        <v>11.2</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="20">
@@ -672,50 +672,50 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Inactif / Retraité</t>
         </is>
       </c>
       <c r="C20">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D20">
-        <v>15.7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ambohidrony</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="C21">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D21">
-        <v>6.7</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ambohidrony</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="C22">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D22">
-        <v>10.7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="23">
@@ -726,14 +726,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="C23">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="D23">
-        <v>36</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="24">
@@ -744,14 +744,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="C24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D24">
-        <v>9.300000000000001</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="25">
@@ -762,14 +762,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Elève / Etudiant</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C25">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="D25">
-        <v>6.7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26">
@@ -780,14 +780,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="C26">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D26">
-        <v>18.7</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -798,56 +798,62 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="C27">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D27">
-        <v>12</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Analamiranga</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
-        </is>
+          <t>Inactif / Retraité</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>6</v>
+      </c>
+      <c r="D28">
+        <v>8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Analamiranga</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
-        </is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>14</v>
+      </c>
+      <c r="D29">
+        <v>18.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Analamiranga</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
-      </c>
-      <c r="C30">
-        <v>37</v>
-      </c>
-      <c r="D30">
-        <v>56.1</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -858,14 +864,8 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Elève / Etudiant</t>
-        </is>
-      </c>
-      <c r="C31">
-        <v>5</v>
-      </c>
-      <c r="D31">
-        <v>7.6</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -876,14 +876,8 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="C32">
-        <v>6</v>
-      </c>
-      <c r="D32">
-        <v>9.1</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -894,80 +888,80 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C33">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="D33">
-        <v>16.7</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Avaradrano</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
-        </is>
+          <t>Elève / Etudiant</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>5</v>
+      </c>
+      <c r="D34">
+        <v>7.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Avaradrano</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
-        </is>
-      </c>
-      <c r="C35">
-        <v>13</v>
-      </c>
-      <c r="D35">
-        <v>10.8</v>
+          <t>Inactif / Retraité</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Avaradrano</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="C36">
-        <v>78</v>
+        <v>6</v>
       </c>
       <c r="D36">
-        <v>65</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Avaradrano</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="C37">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D37">
-        <v>4.2</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="38">
@@ -978,14 +972,8 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Elève / Etudiant</t>
-        </is>
-      </c>
-      <c r="C38">
-        <v>5</v>
-      </c>
-      <c r="D38">
-        <v>4.2</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -996,8 +984,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
+          <t>Commerce &amp; Restauration</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>13</v>
+      </c>
+      <c r="D39">
+        <v>10.8</v>
       </c>
     </row>
     <row r="40">
@@ -1008,92 +1002,98 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C40">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="D40">
-        <v>12.5</v>
+        <v>65</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Feramanga Atsimo</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
-        </is>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>5</v>
+      </c>
+      <c r="D41">
+        <v>4.2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Feramanga Atsimo</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="C42">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D42">
-        <v>10.4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Feramanga Atsimo</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
+          <t>Inactif / Retraité</t>
         </is>
       </c>
       <c r="C43">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="D43">
-        <v>57</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Feramanga Atsimo</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Feramanga Atsimo</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Elève / Etudiant</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="C45">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D45">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="46">
@@ -1104,14 +1104,8 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="C46">
-        <v>15</v>
-      </c>
-      <c r="D46">
-        <v>11.1</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -1122,110 +1116,116 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="C47">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D47">
-        <v>9.6</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mangabe</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>77</v>
+      </c>
+      <c r="D48">
+        <v>57</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Mangabe</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
-        </is>
-      </c>
-      <c r="C49">
-        <v>7</v>
-      </c>
-      <c r="D49">
-        <v>6.4</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Mangabe</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="C50">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="D50">
-        <v>63.6</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Mangabe</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
-        </is>
+          <t>Inactif / Retraité</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>6</v>
+      </c>
+      <c r="D51">
+        <v>4.4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Mangabe</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Elève / Etudiant</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="C52">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D52">
-        <v>10.9</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Mangabe</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="C53">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D53">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="54">
@@ -1236,110 +1236,98 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
-        </is>
-      </c>
-      <c r="C54">
-        <v>10</v>
-      </c>
-      <c r="D54">
-        <v>9.1</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="C55">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="D55">
-        <v>3.9</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C56">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D56">
-        <v>9.9</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
-      </c>
-      <c r="C57">
-        <v>391</v>
-      </c>
-      <c r="D57">
-        <v>52.9</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="C58">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="D58">
-        <v>4.7</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Elève / Etudiant</t>
+          <t>Inactif / Retraité</t>
         </is>
       </c>
       <c r="C59">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="D59">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1348,28 +1336,166 @@
         </is>
       </c>
       <c r="C60">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="D60">
-        <v>10.3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>Mangabe</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>Tous</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>29</v>
+      </c>
+      <c r="D62">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Commerce &amp; Restauration</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>73</v>
+      </c>
+      <c r="D63">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>391</v>
+      </c>
+      <c r="D64">
+        <v>52.9</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>35</v>
+      </c>
+      <c r="D65">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Elève / Etudiant</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>51</v>
+      </c>
+      <c r="D66">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Inactif / Retraité</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>46</v>
+      </c>
+      <c r="D67">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>76</v>
+      </c>
+      <c r="D68">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
         <is>
           <t>Services &amp; Autres</t>
         </is>
       </c>
-      <c r="C61">
-        <v>84</v>
-      </c>
-      <c r="D61">
-        <v>11.4</v>
+      <c r="C69">
+        <v>38</v>
+      </c>
+      <c r="D69">
+        <v>5.1</v>
       </c>
     </row>
   </sheetData>
